--- a/ig/DM-SEPTEMBRE-2025/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/DM-SEPTEMBRE-2025/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2399" uniqueCount="2397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2411" uniqueCount="2409">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250625120000</t>
+    <t>20250919120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-25T12:00:00+01:00</t>
+    <t>2025-09-19T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -291,12 +291,6 @@
     <t>Chirurgie carcinologique gynécologique</t>
   </si>
   <si>
-    <t>0055</t>
-  </si>
-  <si>
-    <t>Chirurgie carcinologique maxillo-faciale et stomatologique</t>
-  </si>
-  <si>
     <t>0056</t>
   </si>
   <si>
@@ -1338,7 +1332,7 @@
     <t>0384</t>
   </si>
   <si>
-    <t>Prélèvement d'organes à coeur battant</t>
+    <t>Prélèvement d'organes à coeur battant (mort cérébrale)</t>
   </si>
   <si>
     <t>0385</t>
@@ -1413,12 +1407,6 @@
     <t>Rééducation basse vision</t>
   </si>
   <si>
-    <t>0413</t>
-  </si>
-  <si>
-    <t>Rééducation orthoptique</t>
-  </si>
-  <si>
     <t>0415</t>
   </si>
   <si>
@@ -1533,12 +1521,6 @@
     <t>Scintigraphie SPECT-CT</t>
   </si>
   <si>
-    <t>0440</t>
-  </si>
-  <si>
-    <t>Soins odontologiques sous anesthésie générale (AG)</t>
-  </si>
-  <si>
     <t>0441</t>
   </si>
   <si>
@@ -2763,12 +2745,6 @@
     <t>Suivi de grossesse à risque</t>
   </si>
   <si>
-    <t>0731</t>
-  </si>
-  <si>
-    <t>Surveillance du nouveau-né à risque</t>
-  </si>
-  <si>
     <t>0732</t>
   </si>
   <si>
@@ -3198,7 +3174,7 @@
     <t>0810</t>
   </si>
   <si>
-    <t>Préparation à la naissance et à la parentalité</t>
+    <t>Séance de préparation à la naissance et à la parentalité en groupe</t>
   </si>
   <si>
     <t>0812</t>
@@ -3669,12 +3645,6 @@
     <t>Réadaptation vésico-sphinctérienne</t>
   </si>
   <si>
-    <t>0893</t>
-  </si>
-  <si>
-    <t>Réadaptation des fonctions sexuelles et de la reproduction</t>
-  </si>
-  <si>
     <t>0894</t>
   </si>
   <si>
@@ -3846,7 +3816,7 @@
     <t>0932</t>
   </si>
   <si>
-    <t>Tests Rapides d'Orientation Diagnostique (TROD)</t>
+    <t>Test Rapide d’Orientation Diagnostique (TROD) VIH / Hépatite B / Hépatite C</t>
   </si>
   <si>
     <t>0958</t>
@@ -4761,12 +4731,6 @@
     <t>Test au baclofène intrathécal</t>
   </si>
   <si>
-    <t>1113</t>
-  </si>
-  <si>
-    <t>Thérapie manuelle</t>
-  </si>
-  <si>
     <t>1114</t>
   </si>
   <si>
@@ -6870,7 +6834,7 @@
     <t>1484</t>
   </si>
   <si>
-    <t>Télésurveillance médicale de l'insuffisance rénale</t>
+    <t>Télésurveillance médicale de la maladie rénale chronique (MRC)</t>
   </si>
   <si>
     <t>1485</t>
@@ -7195,6 +7159,78 @@
   </si>
   <si>
     <t>Vaccination épidémie Covid</t>
+  </si>
+  <si>
+    <t>1539</t>
+  </si>
+  <si>
+    <t>Test Rapide d’Orientation Diagnostique (TROD) Covid-19</t>
+  </si>
+  <si>
+    <t>1540</t>
+  </si>
+  <si>
+    <t>Test Rapide d’Orientation Diagnostique (TROD) Grippe</t>
+  </si>
+  <si>
+    <t>1541</t>
+  </si>
+  <si>
+    <t>Test Rapide d’Orientation Diagnostique (TROD) Virus respiratoire syncytial (VRS)</t>
+  </si>
+  <si>
+    <t>1542</t>
+  </si>
+  <si>
+    <t>Test Rapide d’Orientation Diagnostique (TROD) Angine</t>
+  </si>
+  <si>
+    <t>1543</t>
+  </si>
+  <si>
+    <t>Test Rapide d’Orientation Diagnostique (TROD) Syphilis</t>
+  </si>
+  <si>
+    <t>1544</t>
+  </si>
+  <si>
+    <t>Test Rapide d’Orientation Diagnostique (TROD) Cystite</t>
+  </si>
+  <si>
+    <t>1545</t>
+  </si>
+  <si>
+    <t>Chirurgie de l’allongement osseux</t>
+  </si>
+  <si>
+    <t>1546</t>
+  </si>
+  <si>
+    <t>Correction des malformations congénitales de la main</t>
+  </si>
+  <si>
+    <t>1547</t>
+  </si>
+  <si>
+    <t>Accueil saisonnier possible</t>
+  </si>
+  <si>
+    <t>1548</t>
+  </si>
+  <si>
+    <t>Accueil saisonnier uniquement</t>
+  </si>
+  <si>
+    <t>1549</t>
+  </si>
+  <si>
+    <t>Autodialyse simple</t>
+  </si>
+  <si>
+    <t>1550</t>
+  </si>
+  <si>
+    <t>Autodialyse assistée</t>
   </si>
   <si>
     <t/>
@@ -7465,7 +7501,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1186"/>
+  <dimension ref="A1:B1192"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -16949,15 +16985,63 @@
         <v>2394</v>
       </c>
       <c r="B1185" t="s" s="2">
-        <v>2394</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="1186">
       <c r="A1186" t="s" s="2">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="B1186" t="s" s="2">
-        <v>2396</v>
+        <v>2397</v>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="s" s="2">
+        <v>2398</v>
+      </c>
+      <c r="B1187" t="s" s="2">
+        <v>2399</v>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="s" s="2">
+        <v>2400</v>
+      </c>
+      <c r="B1188" t="s" s="2">
+        <v>2401</v>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="s" s="2">
+        <v>2402</v>
+      </c>
+      <c r="B1189" t="s" s="2">
+        <v>2403</v>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="s" s="2">
+        <v>2404</v>
+      </c>
+      <c r="B1190" t="s" s="2">
+        <v>2405</v>
+      </c>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="s" s="2">
+        <v>2406</v>
+      </c>
+      <c r="B1191" t="s" s="2">
+        <v>2406</v>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="s" s="2">
+        <v>2407</v>
+      </c>
+      <c r="B1192" t="s" s="2">
+        <v>2408</v>
       </c>
     </row>
   </sheetData>
